--- a/StructureDefinition-research-web-Link.xlsx
+++ b/StructureDefinition-research-web-Link.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
